--- a/T8/Fahkumram_Tekken_8_Combos.xlsx
+++ b/T8/Fahkumram_Tekken_8_Combos.xlsx
@@ -581,7 +581,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>★ means neutral (no input). Without it, f, f+4 will be inputted instead. Standard version without just-frame on 3rd hit.</t>
+          <t>n means neutral (no input). Without it, f, f+4 will be inputted instead. Standard version without just-frame on 3rd hit.</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
